--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.55096772422527</v>
+        <v>5.939532255186607</v>
       </c>
       <c r="D2" t="n">
-        <v>34.09381736072883</v>
+        <v>5.540245321118435</v>
       </c>
       <c r="E2" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F2" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.97529713005144</v>
+        <v>6.65848578363336</v>
       </c>
       <c r="D3" t="n">
-        <v>41.97489177654855</v>
+        <v>6.820919913689139</v>
       </c>
       <c r="E3" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F3" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.34288579873332</v>
+        <v>4.930718942294165</v>
       </c>
       <c r="D4" t="n">
-        <v>31.25874675299552</v>
+        <v>5.079546347361772</v>
       </c>
       <c r="E4" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F4" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.31562526757175</v>
+        <v>1.83878910598041</v>
       </c>
       <c r="D5" t="n">
-        <v>11.29351526257968</v>
+        <v>1.835196230169198</v>
       </c>
       <c r="E5" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F5" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.52122550141479</v>
+        <v>3.822199143979903</v>
       </c>
       <c r="D6" t="n">
-        <v>22.67039411889284</v>
+        <v>3.683939044320087</v>
       </c>
       <c r="E6" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F6" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.70068046883117</v>
+        <v>6.613860576185065</v>
       </c>
       <c r="D7" t="n">
-        <v>39.69806979065967</v>
+        <v>6.450936340982196</v>
       </c>
       <c r="E7" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F7" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.54574717791789</v>
+        <v>3.501183916411658</v>
       </c>
       <c r="D8" t="n">
-        <v>21.65293125952821</v>
+        <v>3.518601329673334</v>
       </c>
       <c r="E8" t="n">
-        <v>10.26025283021347</v>
+        <v>1.667291084909688</v>
       </c>
       <c r="F8" t="n">
-        <v>10.15163664362225</v>
+        <v>1.649640954588616</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
